--- a/src/test/resources/testdata/testdata.xlsx
+++ b/src/test/resources/testdata/testdata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2497748\DisplayBookshelves\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B31FD347-7B03-4F9D-BD72-A0372DD0C32E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E65DC10-34BD-4320-A8BA-DAA40224A92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="11840" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="giftcardinput" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
   <si>
     <t>Amount</t>
   </si>
@@ -90,16 +90,39 @@
   </si>
   <si>
     <t>Happy Anniversary</t>
+  </si>
+  <si>
+    <t>Premkumar</t>
+  </si>
+  <si>
+    <t>hasvufdy</t>
+  </si>
+  <si>
+    <t>Shivani</t>
+  </si>
+  <si>
+    <t>shivani@gmail.com</t>
+  </si>
+  <si>
+    <t>HEYYY!!!!!</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -122,13 +145,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -429,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.81640625" customWidth="1"/>
@@ -440,7 +466,7 @@
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="19.54296875" customWidth="1"/>
     <col min="8" max="8" width="16.453125" customWidth="1"/>
-    <col min="9" max="9" width="14.81640625" customWidth="1"/>
+    <col min="9" max="9" width="17.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -507,7 +533,42 @@
         <v>17</v>
       </c>
     </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>1800</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3">
+        <v>7354562543</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I3" r:id="rId1" xr:uid="{59A745ED-0C0A-425F-AAD4-594B6351E4F7}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>